--- a/Documents/courier_rates_2.xlsx
+++ b/Documents/courier_rates_2.xlsx
@@ -24,13 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="90">
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">customer_id</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="88">
   <si>
     <t xml:space="preserve">service_id</t>
   </si>
@@ -694,13 +688,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="true">
+  <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N300"/>
   <sheetFormatPr defaultColWidth="13.4765625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.87"/>
@@ -719,46 +714,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>2</v>
       </c>
@@ -775,7 +770,7 @@
         <v>0.1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>2000</v>
@@ -790,7 +785,7 @@
         <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L2" s="1" t="n">
         <v>1</v>
@@ -802,7 +797,7 @@
         <v>46205.5233449074</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>3</v>
       </c>
@@ -819,7 +814,7 @@
         <v>0.25</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>1900</v>
@@ -828,13 +823,13 @@
         <v>500</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J3" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L3" s="1" t="n">
         <v>1</v>
@@ -846,7 +841,7 @@
         <v>46185.4907407407</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>4</v>
       </c>
@@ -863,7 +858,7 @@
         <v>0.5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>2050</v>
@@ -872,13 +867,13 @@
         <v>500</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J4" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L4" s="1" t="n">
         <v>1</v>
@@ -890,7 +885,7 @@
         <v>46185.4907407407</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>5</v>
       </c>
@@ -907,7 +902,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>2425</v>
@@ -916,13 +911,13 @@
         <v>500</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J5" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L5" s="1" t="n">
         <v>1</v>
@@ -934,7 +929,7 @@
         <v>46185.4907407407</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>6</v>
       </c>
@@ -951,7 +946,7 @@
         <v>1.5</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>2800</v>
@@ -960,13 +955,13 @@
         <v>500</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J6" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L6" s="1" t="n">
         <v>1</v>
@@ -978,7 +973,7 @@
         <v>46185.4907407407</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>7</v>
       </c>
@@ -995,7 +990,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>3125</v>
@@ -1004,13 +999,13 @@
         <v>500</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J7" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L7" s="1" t="n">
         <v>1</v>
@@ -1022,7 +1017,7 @@
         <v>46185.4907407407</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>8</v>
       </c>
@@ -1039,7 +1034,7 @@
         <v>2.5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>3475</v>
@@ -1048,13 +1043,13 @@
         <v>500</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J8" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L8" s="1" t="n">
         <v>1</v>
@@ -1066,7 +1061,7 @@
         <v>46185.4907407407</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>9</v>
       </c>
@@ -1083,7 +1078,7 @@
         <v>0.5</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>1450</v>
@@ -1092,13 +1087,13 @@
         <v>500</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J9" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L9" s="1" t="n">
         <v>1</v>
@@ -1110,7 +1105,7 @@
         <v>46185.4907407407</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>10</v>
       </c>
@@ -1127,7 +1122,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1700</v>
@@ -1136,13 +1131,13 @@
         <v>500</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J10" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L10" s="1" t="n">
         <v>1</v>
@@ -1154,7 +1149,7 @@
         <v>46185.4907407407</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>11</v>
       </c>
@@ -1171,7 +1166,7 @@
         <v>1.5</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>2100</v>
@@ -1180,13 +1175,13 @@
         <v>500</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J11" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L11" s="1" t="n">
         <v>1</v>
@@ -1198,7 +1193,7 @@
         <v>46185.4907407407</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>12</v>
       </c>
@@ -1215,7 +1210,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>2400</v>
@@ -1224,13 +1219,13 @@
         <v>500</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J12" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L12" s="1" t="n">
         <v>1</v>
@@ -1242,7 +1237,7 @@
         <v>46185.4907407407</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>13</v>
       </c>
@@ -1259,7 +1254,7 @@
         <v>2.5</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>2700</v>
@@ -1268,13 +1263,13 @@
         <v>500</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J13" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L13" s="1" t="n">
         <v>1</v>
@@ -1286,7 +1281,7 @@
         <v>46185.4907407407</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>14</v>
       </c>
@@ -1303,7 +1298,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>3000</v>
@@ -1312,13 +1307,13 @@
         <v>500</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J14" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L14" s="1" t="n">
         <v>1</v>
@@ -1330,7 +1325,7 @@
         <v>46185.4907407407</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>15</v>
       </c>
@@ -1347,7 +1342,7 @@
         <v>3.5</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>3250</v>
@@ -1356,13 +1351,13 @@
         <v>500</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J15" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L15" s="1" t="n">
         <v>1</v>
@@ -1374,7 +1369,7 @@
         <v>46185.4907407407</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>16</v>
       </c>
@@ -1391,7 +1386,7 @@
         <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>3550</v>
@@ -1400,13 +1395,13 @@
         <v>500</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J16" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L16" s="1" t="n">
         <v>1</v>
@@ -1418,7 +1413,7 @@
         <v>46185.4907407407</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>17</v>
       </c>
@@ -1435,7 +1430,7 @@
         <v>4.5</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>3900</v>
@@ -1444,13 +1439,13 @@
         <v>500</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J17" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L17" s="1" t="n">
         <v>1</v>
@@ -1462,7 +1457,7 @@
         <v>46185.4907407407</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>18</v>
       </c>
@@ -1479,7 +1474,7 @@
         <v>5</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>4150</v>
@@ -1488,13 +1483,13 @@
         <v>500</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J18" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L18" s="1" t="n">
         <v>1</v>
@@ -1506,7 +1501,7 @@
         <v>46185.4907407407</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>19</v>
       </c>
@@ -1532,13 +1527,13 @@
         <v>500</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L19" s="1" t="n">
         <v>1</v>
@@ -1550,7 +1545,7 @@
         <v>46185.4907407407</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>20</v>
       </c>
@@ -1576,13 +1571,13 @@
         <v>500</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L20" s="1" t="n">
         <v>1</v>
@@ -1594,7 +1589,7 @@
         <v>46206.6651967593</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>21</v>
       </c>
@@ -1620,13 +1615,13 @@
         <v>500</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J21" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L21" s="1" t="n">
         <v>1</v>
@@ -1638,7 +1633,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>22</v>
       </c>
@@ -1664,13 +1659,13 @@
         <v>500</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J22" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L22" s="1" t="n">
         <v>1</v>
@@ -1682,7 +1677,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>23</v>
       </c>
@@ -1708,13 +1703,13 @@
         <v>500</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J23" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L23" s="1" t="n">
         <v>1</v>
@@ -1726,7 +1721,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>24</v>
       </c>
@@ -1752,13 +1747,13 @@
         <v>500</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J24" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L24" s="1" t="n">
         <v>1</v>
@@ -1770,7 +1765,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>25</v>
       </c>
@@ -1796,13 +1791,13 @@
         <v>500</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J25" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L25" s="1" t="n">
         <v>1</v>
@@ -1814,7 +1809,7 @@
         <v>46206.6623611111</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>26</v>
       </c>
@@ -1840,13 +1835,13 @@
         <v>500</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J26" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L26" s="1" t="n">
         <v>1</v>
@@ -1858,7 +1853,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>27</v>
       </c>
@@ -1884,13 +1879,13 @@
         <v>500</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J27" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L27" s="1" t="n">
         <v>1</v>
@@ -1902,7 +1897,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>28</v>
       </c>
@@ -1928,13 +1923,13 @@
         <v>500</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J28" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L28" s="1" t="n">
         <v>1</v>
@@ -1946,7 +1941,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>29</v>
       </c>
@@ -1972,13 +1967,13 @@
         <v>500</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J29" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L29" s="1" t="n">
         <v>1</v>
@@ -1990,7 +1985,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
         <v>30</v>
       </c>
@@ -2016,13 +2011,13 @@
         <v>500</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J30" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L30" s="1" t="n">
         <v>1</v>
@@ -2034,7 +2029,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
         <v>31</v>
       </c>
@@ -2051,7 +2046,7 @@
         <v>0.05</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>580</v>
@@ -2060,13 +2055,13 @@
         <v>500</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J31" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L31" s="1" t="n">
         <v>1</v>
@@ -2078,7 +2073,7 @@
         <v>46198.6075231481</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
         <v>32</v>
       </c>
@@ -2095,7 +2090,7 @@
         <v>0.1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>620</v>
@@ -2104,13 +2099,13 @@
         <v>500</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J32" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L32" s="1" t="n">
         <v>1</v>
@@ -2122,7 +2117,7 @@
         <v>46198.6075231481</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>33</v>
       </c>
@@ -2139,7 +2134,7 @@
         <v>0.15</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>675</v>
@@ -2148,13 +2143,13 @@
         <v>500</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J33" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L33" s="1" t="n">
         <v>1</v>
@@ -2166,7 +2161,7 @@
         <v>46198.6075231481</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
         <v>34</v>
       </c>
@@ -2183,7 +2178,7 @@
         <v>0.2</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>725</v>
@@ -2192,13 +2187,13 @@
         <v>500</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J34" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L34" s="1" t="n">
         <v>1</v>
@@ -2210,7 +2205,7 @@
         <v>46198.6075231481</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
         <v>35</v>
       </c>
@@ -2227,7 +2222,7 @@
         <v>0.25</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G35" s="6" t="n">
         <v>825</v>
@@ -2236,13 +2231,13 @@
         <v>500</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J35" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L35" s="1" t="n">
         <v>1</v>
@@ -2254,7 +2249,7 @@
         <v>46198.6075231481</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
         <v>36</v>
       </c>
@@ -2271,7 +2266,7 @@
         <v>0.3</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>900</v>
@@ -2280,13 +2275,13 @@
         <v>500</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J36" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L36" s="1" t="n">
         <v>1</v>
@@ -2298,7 +2293,7 @@
         <v>46198.6075231481</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="n">
         <v>37</v>
       </c>
@@ -2315,7 +2310,7 @@
         <v>0.35</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>980</v>
@@ -2324,13 +2319,13 @@
         <v>500</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J37" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L37" s="1" t="n">
         <v>1</v>
@@ -2342,7 +2337,7 @@
         <v>46198.6075231481</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
         <v>38</v>
       </c>
@@ -2359,7 +2354,7 @@
         <v>0.4</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>1030</v>
@@ -2368,13 +2363,13 @@
         <v>500</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J38" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L38" s="1" t="n">
         <v>1</v>
@@ -2386,7 +2381,7 @@
         <v>46198.6075231481</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="n">
         <v>39</v>
       </c>
@@ -2403,7 +2398,7 @@
         <v>0.5</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>1500</v>
@@ -2412,13 +2407,13 @@
         <v>500</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J39" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L39" s="1" t="n">
         <v>1</v>
@@ -2430,7 +2425,7 @@
         <v>46198.6075231481</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="n">
         <v>40</v>
       </c>
@@ -2447,7 +2442,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>1950</v>
@@ -2456,13 +2451,13 @@
         <v>500</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J40" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L40" s="1" t="n">
         <v>1</v>
@@ -2474,7 +2469,7 @@
         <v>46198.6075231481</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="n">
         <v>41</v>
       </c>
@@ -2491,7 +2486,7 @@
         <v>1.5</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>2350</v>
@@ -2500,13 +2495,13 @@
         <v>500</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J41" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>1</v>
@@ -2518,7 +2513,7 @@
         <v>46198.6075231481</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="n">
         <v>42</v>
       </c>
@@ -2535,7 +2530,7 @@
         <v>2</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>2900</v>
@@ -2544,13 +2539,13 @@
         <v>500</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J42" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L42" s="1" t="n">
         <v>1</v>
@@ -2562,7 +2557,7 @@
         <v>46198.6075231481</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="n">
         <v>43</v>
       </c>
@@ -2579,7 +2574,7 @@
         <v>2.5</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>3650</v>
@@ -2588,13 +2583,13 @@
         <v>500</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J43" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L43" s="1" t="n">
         <v>1</v>
@@ -2606,7 +2601,7 @@
         <v>46198.6075231481</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="n">
         <v>44</v>
       </c>
@@ -2623,7 +2618,7 @@
         <v>3</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>4250</v>
@@ -2632,13 +2627,13 @@
         <v>500</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J44" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L44" s="1" t="n">
         <v>1</v>
@@ -2650,7 +2645,7 @@
         <v>46198.6075231481</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="n">
         <v>45</v>
       </c>
@@ -2667,7 +2662,7 @@
         <v>3.5</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>4675</v>
@@ -2676,13 +2671,13 @@
         <v>500</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J45" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L45" s="1" t="n">
         <v>1</v>
@@ -2694,7 +2689,7 @@
         <v>46198.6075231481</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="n">
         <v>46</v>
       </c>
@@ -2711,7 +2706,7 @@
         <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>5125</v>
@@ -2720,13 +2715,13 @@
         <v>500</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J46" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L46" s="1" t="n">
         <v>1</v>
@@ -2738,7 +2733,7 @@
         <v>46198.6075231481</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="n">
         <v>47</v>
       </c>
@@ -2755,7 +2750,7 @@
         <v>4.5</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>5560</v>
@@ -2764,13 +2759,13 @@
         <v>500</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J47" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L47" s="1" t="n">
         <v>1</v>
@@ -2782,7 +2777,7 @@
         <v>46198.6075231481</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="n">
         <v>48</v>
       </c>
@@ -2799,7 +2794,7 @@
         <v>5</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>6000</v>
@@ -2808,13 +2803,13 @@
         <v>500</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J48" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L48" s="1" t="n">
         <v>1</v>
@@ -2837,13 +2832,13 @@
         <v>8</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E49" s="8" t="n">
         <v>50</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>375</v>
@@ -2852,13 +2847,13 @@
         <v>500</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J49" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L49" s="1" t="n">
         <v>1</v>
@@ -2881,13 +2876,13 @@
         <v>8</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E50" s="8" t="n">
         <v>100</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>400</v>
@@ -2896,13 +2891,13 @@
         <v>500</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J50" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L50" s="1" t="n">
         <v>1</v>
@@ -2925,13 +2920,13 @@
         <v>8</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E51" s="8" t="n">
         <v>150</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>450</v>
@@ -2940,13 +2935,13 @@
         <v>500</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J51" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L51" s="1" t="n">
         <v>1</v>
@@ -2969,13 +2964,13 @@
         <v>8</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E52" s="8" t="n">
         <v>200</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G52" s="9" t="n">
         <v>500</v>
@@ -2984,13 +2979,13 @@
         <v>500</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J52" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L52" s="1" t="n">
         <v>1</v>
@@ -3013,13 +3008,13 @@
         <v>8</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E53" s="8" t="n">
         <v>250</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>550</v>
@@ -3028,13 +3023,13 @@
         <v>500</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J53" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L53" s="1" t="n">
         <v>1</v>
@@ -3057,13 +3052,13 @@
         <v>8</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E54" s="8" t="n">
         <v>300</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G54" s="9" t="n">
         <v>590</v>
@@ -3072,13 +3067,13 @@
         <v>500</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J54" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L54" s="1" t="n">
         <v>1</v>
@@ -3101,13 +3096,13 @@
         <v>8</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E55" s="8" t="n">
         <v>350</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G55" s="9" t="n">
         <v>645</v>
@@ -3116,13 +3111,13 @@
         <v>500</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J55" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L55" s="1" t="n">
         <v>1</v>
@@ -3145,13 +3140,13 @@
         <v>8</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E56" s="8" t="n">
         <v>400</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G56" s="9" t="n">
         <v>690</v>
@@ -3160,13 +3155,13 @@
         <v>500</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J56" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L56" s="1" t="n">
         <v>1</v>
@@ -3189,13 +3184,13 @@
         <v>8</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E57" s="8" t="n">
         <v>450</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>750</v>
@@ -3204,13 +3199,13 @@
         <v>500</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J57" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L57" s="1" t="n">
         <v>1</v>
@@ -3233,13 +3228,13 @@
         <v>8</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E58" s="8" t="n">
         <v>500</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G58" s="9" t="n">
         <v>795</v>
@@ -3248,13 +3243,13 @@
         <v>500</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J58" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L58" s="1" t="n">
         <v>1</v>
@@ -3277,13 +3272,13 @@
         <v>8</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E59" s="8" t="n">
         <v>600</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G59" s="9" t="n">
         <v>880</v>
@@ -3292,13 +3287,13 @@
         <v>500</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J59" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L59" s="1" t="n">
         <v>1</v>
@@ -3321,13 +3316,13 @@
         <v>8</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E60" s="8" t="n">
         <v>700</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G60" s="9" t="n">
         <v>970</v>
@@ -3336,13 +3331,13 @@
         <v>500</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J60" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L60" s="1" t="n">
         <v>1</v>
@@ -3365,13 +3360,13 @@
         <v>8</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E61" s="8" t="n">
         <v>800</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G61" s="9" t="n">
         <v>1140</v>
@@ -3380,13 +3375,13 @@
         <v>500</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J61" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L61" s="1" t="n">
         <v>1</v>
@@ -3409,13 +3404,13 @@
         <v>8</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E62" s="8" t="n">
         <v>900</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G62" s="9" t="n">
         <v>1230</v>
@@ -3424,13 +3419,13 @@
         <v>500</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J62" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L62" s="1" t="n">
         <v>1</v>
@@ -3453,13 +3448,13 @@
         <v>8</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E63" s="8" t="n">
         <v>1000</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>1320</v>
@@ -3468,13 +3463,13 @@
         <v>500</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J63" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L63" s="1" t="n">
         <v>1</v>
@@ -3497,13 +3492,13 @@
         <v>8</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E64" s="8" t="n">
         <v>1100</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>1620</v>
@@ -3512,13 +3507,13 @@
         <v>500</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J64" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L64" s="1" t="n">
         <v>1</v>
@@ -3541,13 +3536,13 @@
         <v>8</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E65" s="8" t="n">
         <v>1200</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>1710</v>
@@ -3556,13 +3551,13 @@
         <v>500</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J65" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L65" s="1" t="n">
         <v>1</v>
@@ -3585,13 +3580,13 @@
         <v>8</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E66" s="8" t="n">
         <v>1300</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G66" s="9" t="n">
         <v>1805</v>
@@ -3600,13 +3595,13 @@
         <v>500</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J66" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L66" s="1" t="n">
         <v>1</v>
@@ -3629,13 +3624,13 @@
         <v>8</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E67" s="8" t="n">
         <v>1400</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G67" s="9" t="n">
         <v>1890</v>
@@ -3644,13 +3639,13 @@
         <v>500</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J67" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L67" s="1" t="n">
         <v>1</v>
@@ -3673,13 +3668,13 @@
         <v>8</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E68" s="8" t="n">
         <v>1500</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G68" s="9" t="n">
         <v>1975</v>
@@ -3688,13 +3683,13 @@
         <v>500</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J68" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L68" s="1" t="n">
         <v>1</v>
@@ -3717,13 +3712,13 @@
         <v>8</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E69" s="8" t="n">
         <v>1600</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G69" s="9" t="n">
         <v>2225</v>
@@ -3732,13 +3727,13 @@
         <v>500</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J69" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L69" s="1" t="n">
         <v>1</v>
@@ -3761,13 +3756,13 @@
         <v>8</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E70" s="8" t="n">
         <v>1700</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>2210</v>
@@ -3776,13 +3771,13 @@
         <v>500</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J70" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L70" s="1" t="n">
         <v>1</v>
@@ -3805,13 +3800,13 @@
         <v>8</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E71" s="8" t="n">
         <v>1800</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>2400</v>
@@ -3820,13 +3815,13 @@
         <v>500</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J71" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L71" s="1" t="n">
         <v>1</v>
@@ -3849,13 +3844,13 @@
         <v>8</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E72" s="8" t="n">
         <v>1900</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>2475</v>
@@ -3864,13 +3859,13 @@
         <v>500</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J72" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L72" s="1" t="n">
         <v>1</v>
@@ -3893,13 +3888,13 @@
         <v>8</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E73" s="8" t="n">
         <v>2000</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G73" s="9" t="n">
         <v>2580</v>
@@ -3908,13 +3903,13 @@
         <v>500</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J73" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L73" s="1" t="n">
         <v>1</v>
@@ -3926,7 +3921,7 @@
         <v>46198.6075231481</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="n">
         <v>74</v>
       </c>
@@ -3943,22 +3938,22 @@
         <v>0.5</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G74" s="1" t="n">
         <v>825</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L74" s="1" t="n">
         <v>1</v>
@@ -3970,7 +3965,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="n">
         <v>75</v>
       </c>
@@ -3987,22 +3982,22 @@
         <v>1</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G75" s="1" t="n">
         <v>1075</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L75" s="1" t="n">
         <v>1</v>
@@ -4014,7 +4009,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="n">
         <v>76</v>
       </c>
@@ -4031,22 +4026,22 @@
         <v>2</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G76" s="1" t="n">
         <v>1325</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L76" s="1" t="n">
         <v>1</v>
@@ -4058,7 +4053,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="n">
         <v>77</v>
       </c>
@@ -4075,22 +4070,22 @@
         <v>3</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G77" s="1" t="n">
         <v>1825</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L77" s="1" t="n">
         <v>1</v>
@@ -4102,7 +4097,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="n">
         <v>78</v>
       </c>
@@ -4119,22 +4114,22 @@
         <v>2.5</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G78" s="1" t="n">
         <v>2075</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L78" s="1" t="n">
         <v>1</v>
@@ -4146,7 +4141,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="n">
         <v>79</v>
       </c>
@@ -4163,22 +4158,22 @@
         <v>3</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G79" s="1" t="n">
         <v>2325</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L79" s="1" t="n">
         <v>1</v>
@@ -4190,7 +4185,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="n">
         <v>80</v>
       </c>
@@ -4207,22 +4202,22 @@
         <v>3.5</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G80" s="1" t="n">
         <v>1325</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L80" s="1" t="n">
         <v>1</v>
@@ -4234,7 +4229,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="n">
         <v>81</v>
       </c>
@@ -4251,22 +4246,22 @@
         <v>4</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G81" s="1" t="n">
         <v>1825</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L81" s="1" t="n">
         <v>1</v>
@@ -4278,7 +4273,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="n">
         <v>82</v>
       </c>
@@ -4295,22 +4290,22 @@
         <v>4.5</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G82" s="1" t="n">
         <v>2075</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L82" s="1" t="n">
         <v>1</v>
@@ -4322,7 +4317,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="n">
         <v>83</v>
       </c>
@@ -4339,22 +4334,22 @@
         <v>5</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G83" s="1" t="n">
         <v>2325</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L83" s="1" t="n">
         <v>1</v>
@@ -4366,7 +4361,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="n">
         <v>84</v>
       </c>
@@ -4383,23 +4378,23 @@
         <v>6</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G84" s="1" t="n">
         <f aca="false">495*E84</f>
         <v>2970</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L84" s="1" t="n">
         <v>1</v>
@@ -4411,7 +4406,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="n">
         <v>85</v>
       </c>
@@ -4428,23 +4423,23 @@
         <v>7</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G85" s="1" t="n">
         <f aca="false">495*E85</f>
         <v>3465</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L85" s="1" t="n">
         <v>1</v>
@@ -4456,7 +4451,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="n">
         <v>86</v>
       </c>
@@ -4473,23 +4468,23 @@
         <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G86" s="1" t="n">
         <f aca="false">495*E86</f>
         <v>3960</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L86" s="1" t="n">
         <v>1</v>
@@ -4501,7 +4496,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="n">
         <v>87</v>
       </c>
@@ -4518,23 +4513,23 @@
         <v>9</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G87" s="1" t="n">
         <f aca="false">455*E87</f>
         <v>4095</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L87" s="1" t="n">
         <v>1</v>
@@ -4546,7 +4541,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="n">
         <v>88</v>
       </c>
@@ -4563,23 +4558,23 @@
         <v>10</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G88" s="1" t="n">
         <f aca="false">455*E88</f>
         <v>4550</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L88" s="1" t="n">
         <v>1</v>
@@ -4591,7 +4586,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="n">
         <v>89</v>
       </c>
@@ -4608,23 +4603,23 @@
         <v>11</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G89" s="1" t="n">
         <f aca="false">455*E89</f>
         <v>5005</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L89" s="1" t="n">
         <v>1</v>
@@ -4636,7 +4631,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="n">
         <v>90</v>
       </c>
@@ -4653,22 +4648,22 @@
         <v>0.1</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G90" s="1" t="n">
         <v>310</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L90" s="1" t="n">
         <v>1</v>
@@ -4680,7 +4675,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="n">
         <v>91</v>
       </c>
@@ -4697,22 +4692,22 @@
         <v>0.2</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G91" s="1" t="n">
         <v>375</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L91" s="1" t="n">
         <v>1</v>
@@ -4724,7 +4719,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="n">
         <v>92</v>
       </c>
@@ -4741,22 +4736,22 @@
         <v>0.3</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G92" s="1" t="n">
         <v>440</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L92" s="1" t="n">
         <v>1</v>
@@ -4768,7 +4763,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="n">
         <v>93</v>
       </c>
@@ -4785,22 +4780,22 @@
         <v>0.4</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G93" s="1" t="n">
         <v>505</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L93" s="1" t="n">
         <v>1</v>
@@ -4812,7 +4807,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="n">
         <v>94</v>
       </c>
@@ -4829,22 +4824,22 @@
         <v>0.5</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G94" s="1" t="n">
         <v>570</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L94" s="1" t="n">
         <v>1</v>
@@ -4856,7 +4851,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="n">
         <v>95</v>
       </c>
@@ -4873,22 +4868,22 @@
         <v>0.75</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G95" s="1" t="n">
         <v>710</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L95" s="1" t="n">
         <v>1</v>
@@ -4900,7 +4895,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="n">
         <v>96</v>
       </c>
@@ -4917,22 +4912,22 @@
         <v>1</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G96" s="1" t="n">
         <v>895</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L96" s="1" t="n">
         <v>1</v>
@@ -4944,7 +4939,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="n">
         <v>97</v>
       </c>
@@ -4961,22 +4956,22 @@
         <v>1.5</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G97" s="1" t="n">
         <v>1220</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L97" s="1" t="n">
         <v>1</v>
@@ -4988,7 +4983,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="n">
         <v>98</v>
       </c>
@@ -5005,22 +5000,22 @@
         <v>2</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G98" s="1" t="n">
         <v>1550</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L98" s="1" t="n">
         <v>1</v>
@@ -5032,7 +5027,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="n">
         <v>99</v>
       </c>
@@ -5049,22 +5044,22 @@
         <v>2.5</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G99" s="1" t="n">
         <v>1875</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L99" s="1" t="n">
         <v>1</v>
@@ -5076,7 +5071,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="n">
         <v>100</v>
       </c>
@@ -5093,22 +5088,22 @@
         <v>3</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G100" s="1" t="n">
         <v>2195</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L100" s="1" t="n">
         <v>1</v>
@@ -5120,7 +5115,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="n">
         <v>101</v>
       </c>
@@ -5137,22 +5132,22 @@
         <v>3.5</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G101" s="1" t="n">
         <v>3155</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L101" s="1" t="n">
         <v>1</v>
@@ -5164,7 +5159,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="n">
         <v>102</v>
       </c>
@@ -5181,22 +5176,22 @@
         <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G102" s="1" t="n">
         <v>3570</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L102" s="1" t="n">
         <v>1</v>
@@ -5208,7 +5203,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="n">
         <v>103</v>
       </c>
@@ -5225,22 +5220,22 @@
         <v>4.5</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G103" s="1" t="n">
         <v>3985</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L103" s="1" t="n">
         <v>1</v>
@@ -5252,7 +5247,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="n">
         <v>104</v>
       </c>
@@ -5269,22 +5264,22 @@
         <v>5</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G104" s="1" t="n">
         <v>4400</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L104" s="1" t="n">
         <v>1</v>
@@ -5296,7 +5291,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="n">
         <v>105</v>
       </c>
@@ -5322,13 +5317,13 @@
         <v>500</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J105" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L105" s="1" t="n">
         <v>1</v>
@@ -5340,7 +5335,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="n">
         <v>106</v>
       </c>
@@ -5366,13 +5361,13 @@
         <v>500</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J106" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L106" s="1" t="n">
         <v>1</v>
@@ -5384,7 +5379,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="n">
         <v>107</v>
       </c>
@@ -5410,13 +5405,13 @@
         <v>500</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J107" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L107" s="1" t="n">
         <v>1</v>
@@ -5428,7 +5423,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="n">
         <v>108</v>
       </c>
@@ -5455,13 +5450,13 @@
         <v>500</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J108" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L108" s="1" t="n">
         <v>1</v>
@@ -5473,7 +5468,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="n">
         <v>109</v>
       </c>
@@ -5500,13 +5495,13 @@
         <v>500</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J109" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L109" s="1" t="n">
         <v>1</v>
@@ -5518,7 +5513,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="n">
         <v>110</v>
       </c>
@@ -5545,13 +5540,13 @@
         <v>500</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J110" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L110" s="1" t="n">
         <v>1</v>
@@ -5563,7 +5558,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="n">
         <v>111</v>
       </c>
@@ -5590,13 +5585,13 @@
         <v>500</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J111" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L111" s="1" t="n">
         <v>1</v>
@@ -5608,7 +5603,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="n">
         <v>112</v>
       </c>
@@ -5635,13 +5630,13 @@
         <v>500</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J112" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L112" s="1" t="n">
         <v>1</v>
@@ -5653,7 +5648,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="n">
         <v>113</v>
       </c>
@@ -5680,13 +5675,13 @@
         <v>500</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J113" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L113" s="1" t="n">
         <v>1</v>
@@ -5698,7 +5693,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="n">
         <v>114</v>
       </c>
@@ -5725,13 +5720,13 @@
         <v>500</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J114" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L114" s="1" t="n">
         <v>1</v>
@@ -5743,7 +5738,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="n">
         <v>115</v>
       </c>
@@ -5770,13 +5765,13 @@
         <v>500</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J115" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L115" s="1" t="n">
         <v>1</v>
@@ -5788,7 +5783,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="n">
         <v>116</v>
       </c>
@@ -5815,13 +5810,13 @@
         <v>500</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J116" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L116" s="1" t="n">
         <v>1</v>
@@ -5833,7 +5828,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="n">
         <v>117</v>
       </c>
@@ -5860,13 +5855,13 @@
         <v>500</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J117" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L117" s="1" t="n">
         <v>1</v>
@@ -5878,7 +5873,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="n">
         <v>118</v>
       </c>
@@ -5905,13 +5900,13 @@
         <v>500</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J118" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L118" s="1" t="n">
         <v>1</v>
@@ -5923,7 +5918,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="n">
         <v>119</v>
       </c>
@@ -5950,13 +5945,13 @@
         <v>500</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J119" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L119" s="1" t="n">
         <v>1</v>
@@ -5968,7 +5963,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="n">
         <v>120</v>
       </c>
@@ -5994,13 +5989,13 @@
         <v>500</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J120" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L120" s="1" t="n">
         <v>1</v>
@@ -6012,7 +6007,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="n">
         <v>121</v>
       </c>
@@ -6038,13 +6033,13 @@
         <v>500</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J121" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L121" s="1" t="n">
         <v>1</v>
@@ -6056,7 +6051,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="n">
         <v>122</v>
       </c>
@@ -6082,13 +6077,13 @@
         <v>500</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J122" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L122" s="1" t="n">
         <v>1</v>
@@ -6100,7 +6095,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="n">
         <v>123</v>
       </c>
@@ -6126,13 +6121,13 @@
         <v>500</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J123" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L123" s="1" t="n">
         <v>1</v>
@@ -6144,7 +6139,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="n">
         <v>124</v>
       </c>
@@ -6170,13 +6165,13 @@
         <v>500</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J124" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L124" s="1" t="n">
         <v>1</v>
@@ -6188,7 +6183,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="n">
         <v>125</v>
       </c>
@@ -6214,13 +6209,13 @@
         <v>500</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J125" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L125" s="1" t="n">
         <v>1</v>
@@ -6232,7 +6227,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="n">
         <v>126</v>
       </c>
@@ -6258,13 +6253,13 @@
         <v>500</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J126" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L126" s="1" t="n">
         <v>1</v>
@@ -6276,7 +6271,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="n">
         <v>127</v>
       </c>
@@ -6302,13 +6297,13 @@
         <v>500</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J127" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L127" s="1" t="n">
         <v>1</v>
@@ -6320,7 +6315,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="n">
         <v>128</v>
       </c>
@@ -6346,13 +6341,13 @@
         <v>500</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J128" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L128" s="1" t="n">
         <v>1</v>
@@ -6364,7 +6359,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="n">
         <v>129</v>
       </c>
@@ -6390,13 +6385,13 @@
         <v>500</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J129" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L129" s="1" t="n">
         <v>1</v>
@@ -6408,7 +6403,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="n">
         <v>130</v>
       </c>
@@ -6434,13 +6429,13 @@
         <v>500</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J130" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L130" s="1" t="n">
         <v>1</v>
@@ -6452,7 +6447,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="n">
         <v>131</v>
       </c>
@@ -6478,13 +6473,13 @@
         <v>500</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J131" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L131" s="1" t="n">
         <v>1</v>
@@ -6496,7 +6491,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="n">
         <v>132</v>
       </c>
@@ -6522,13 +6517,13 @@
         <v>500</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J132" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L132" s="1" t="n">
         <v>1</v>
@@ -6540,7 +6535,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="n">
         <v>133</v>
       </c>
@@ -6566,13 +6561,13 @@
         <v>500</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J133" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L133" s="1" t="n">
         <v>1</v>
@@ -6584,7 +6579,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="n">
         <v>134</v>
       </c>
@@ -6610,13 +6605,13 @@
         <v>500</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J134" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L134" s="1" t="n">
         <v>1</v>
@@ -6628,7 +6623,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="n">
         <v>135</v>
       </c>
@@ -6655,13 +6650,13 @@
         <v>500</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J135" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L135" s="1" t="n">
         <v>1</v>
@@ -6673,7 +6668,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="n">
         <v>136</v>
       </c>
@@ -6700,13 +6695,13 @@
         <v>500</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J136" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L136" s="1" t="n">
         <v>1</v>
@@ -6718,7 +6713,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="n">
         <v>137</v>
       </c>
@@ -6745,13 +6740,13 @@
         <v>500</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J137" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K137" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L137" s="1" t="n">
         <v>1</v>
@@ -6763,7 +6758,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="n">
         <v>138</v>
       </c>
@@ -6790,13 +6785,13 @@
         <v>500</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J138" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K138" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L138" s="1" t="n">
         <v>1</v>
@@ -6808,7 +6803,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="n">
         <v>139</v>
       </c>
@@ -6835,13 +6830,13 @@
         <v>500</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J139" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K139" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L139" s="1" t="n">
         <v>1</v>
@@ -6853,7 +6848,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="n">
         <v>140</v>
       </c>
@@ -6880,13 +6875,13 @@
         <v>500</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J140" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K140" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L140" s="1" t="n">
         <v>1</v>
@@ -6898,7 +6893,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="n">
         <v>141</v>
       </c>
@@ -6925,13 +6920,13 @@
         <v>500</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J141" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L141" s="1" t="n">
         <v>1</v>
@@ -6943,7 +6938,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="n">
         <v>142</v>
       </c>
@@ -6970,13 +6965,13 @@
         <v>500</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J142" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K142" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L142" s="1" t="n">
         <v>1</v>
@@ -6988,7 +6983,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="n">
         <v>143</v>
       </c>
@@ -7015,13 +7010,13 @@
         <v>500</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J143" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K143" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L143" s="1" t="n">
         <v>1</v>
@@ -7033,7 +7028,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="n">
         <v>144</v>
       </c>
@@ -7060,13 +7055,13 @@
         <v>500</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J144" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K144" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L144" s="1" t="n">
         <v>1</v>
@@ -7078,7 +7073,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="n">
         <v>145</v>
       </c>
@@ -7105,13 +7100,13 @@
         <v>500</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J145" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K145" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L145" s="1" t="n">
         <v>1</v>
@@ -7123,7 +7118,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="n">
         <v>146</v>
       </c>
@@ -7150,13 +7145,13 @@
         <v>500</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J146" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K146" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L146" s="1" t="n">
         <v>1</v>
@@ -7168,7 +7163,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="n">
         <v>147</v>
       </c>
@@ -7194,13 +7189,13 @@
         <v>500</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J147" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K147" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L147" s="1" t="n">
         <v>1</v>
@@ -7212,7 +7207,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="n">
         <v>148</v>
       </c>
@@ -7238,13 +7233,13 @@
         <v>500</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J148" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K148" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L148" s="1" t="n">
         <v>1</v>
@@ -7256,7 +7251,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="n">
         <v>149</v>
       </c>
@@ -7282,13 +7277,13 @@
         <v>500</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J149" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K149" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L149" s="1" t="n">
         <v>1</v>
@@ -7300,7 +7295,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="n">
         <v>150</v>
       </c>
@@ -7326,13 +7321,13 @@
         <v>500</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J150" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K150" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L150" s="1" t="n">
         <v>1</v>
@@ -7344,7 +7339,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="n">
         <v>151</v>
       </c>
@@ -7370,13 +7365,13 @@
         <v>500</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J151" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K151" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L151" s="1" t="n">
         <v>1</v>
@@ -7388,7 +7383,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="n">
         <v>152</v>
       </c>
@@ -7414,13 +7409,13 @@
         <v>500</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J152" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K152" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L152" s="1" t="n">
         <v>1</v>
@@ -7432,7 +7427,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="n">
         <v>153</v>
       </c>
@@ -7458,13 +7453,13 @@
         <v>500</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J153" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K153" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L153" s="1" t="n">
         <v>1</v>
@@ -7476,7 +7471,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="n">
         <v>154</v>
       </c>
@@ -7502,13 +7497,13 @@
         <v>500</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J154" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K154" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L154" s="1" t="n">
         <v>1</v>
@@ -7520,7 +7515,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="n">
         <v>155</v>
       </c>
@@ -7546,13 +7541,13 @@
         <v>500</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J155" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K155" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L155" s="1" t="n">
         <v>1</v>
@@ -7564,7 +7559,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="n">
         <v>156</v>
       </c>
@@ -7590,13 +7585,13 @@
         <v>500</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J156" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K156" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L156" s="1" t="n">
         <v>1</v>
@@ -7608,7 +7603,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="n">
         <v>157</v>
       </c>
@@ -7634,13 +7629,13 @@
         <v>500</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J157" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K157" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L157" s="1" t="n">
         <v>1</v>
@@ -7652,7 +7647,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="n">
         <v>158</v>
       </c>
@@ -7678,13 +7673,13 @@
         <v>500</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J158" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K158" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L158" s="1" t="n">
         <v>1</v>
@@ -7696,7 +7691,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="n">
         <v>159</v>
       </c>
@@ -7722,13 +7717,13 @@
         <v>500</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J159" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K159" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L159" s="1" t="n">
         <v>1</v>
@@ -7740,7 +7735,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="n">
         <v>160</v>
       </c>
@@ -7766,13 +7761,13 @@
         <v>500</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J160" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K160" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L160" s="1" t="n">
         <v>1</v>
@@ -7784,7 +7779,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="n">
         <v>161</v>
       </c>
@@ -7810,13 +7805,13 @@
         <v>500</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J161" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K161" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L161" s="1" t="n">
         <v>1</v>
@@ -7828,7 +7823,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="n">
         <v>162</v>
       </c>
@@ -7855,13 +7850,13 @@
         <v>500</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J162" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K162" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L162" s="1" t="n">
         <v>1</v>
@@ -7873,7 +7868,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="n">
         <v>163</v>
       </c>
@@ -7900,13 +7895,13 @@
         <v>500</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J163" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K163" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L163" s="1" t="n">
         <v>1</v>
@@ -7918,7 +7913,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="n">
         <v>164</v>
       </c>
@@ -7945,13 +7940,13 @@
         <v>500</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J164" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L164" s="1" t="n">
         <v>1</v>
@@ -7963,7 +7958,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="n">
         <v>165</v>
       </c>
@@ -7990,13 +7985,13 @@
         <v>500</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J165" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K165" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L165" s="1" t="n">
         <v>1</v>
@@ -8008,7 +8003,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="n">
         <v>166</v>
       </c>
@@ -8035,13 +8030,13 @@
         <v>500</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J166" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K166" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L166" s="1" t="n">
         <v>1</v>
@@ -8053,7 +8048,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="n">
         <v>167</v>
       </c>
@@ -8080,13 +8075,13 @@
         <v>500</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J167" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K167" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L167" s="1" t="n">
         <v>1</v>
@@ -8098,7 +8093,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="n">
         <v>168</v>
       </c>
@@ -8125,13 +8120,13 @@
         <v>500</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J168" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K168" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L168" s="1" t="n">
         <v>1</v>
@@ -8143,7 +8138,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="n">
         <v>169</v>
       </c>
@@ -8170,13 +8165,13 @@
         <v>500</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J169" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K169" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L169" s="1" t="n">
         <v>1</v>
@@ -8188,7 +8183,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="n">
         <v>170</v>
       </c>
@@ -8215,13 +8210,13 @@
         <v>500</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J170" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K170" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L170" s="1" t="n">
         <v>1</v>
@@ -8233,7 +8228,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="n">
         <v>171</v>
       </c>
@@ -8260,13 +8255,13 @@
         <v>500</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J171" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K171" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L171" s="1" t="n">
         <v>1</v>
@@ -8278,7 +8273,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="n">
         <v>172</v>
       </c>
@@ -8305,13 +8300,13 @@
         <v>500</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J172" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K172" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L172" s="1" t="n">
         <v>1</v>
@@ -8323,7 +8318,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="n">
         <v>173</v>
       </c>
@@ -8350,13 +8345,13 @@
         <v>500</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J173" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K173" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L173" s="1" t="n">
         <v>1</v>
@@ -8368,7 +8363,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="n">
         <v>174</v>
       </c>
@@ -8394,13 +8389,13 @@
         <v>500</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J174" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K174" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L174" s="1" t="n">
         <v>1</v>
@@ -8412,7 +8407,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="n">
         <v>175</v>
       </c>
@@ -8438,13 +8433,13 @@
         <v>500</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J175" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K175" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L175" s="1" t="n">
         <v>1</v>
@@ -8456,7 +8451,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="n">
         <v>176</v>
       </c>
@@ -8482,13 +8477,13 @@
         <v>500</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J176" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K176" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L176" s="1" t="n">
         <v>1</v>
@@ -8500,7 +8495,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="n">
         <v>177</v>
       </c>
@@ -8526,13 +8521,13 @@
         <v>500</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J177" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K177" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L177" s="1" t="n">
         <v>1</v>
@@ -8544,7 +8539,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="n">
         <v>178</v>
       </c>
@@ -8570,13 +8565,13 @@
         <v>500</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J178" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K178" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L178" s="1" t="n">
         <v>1</v>
@@ -8588,7 +8583,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="n">
         <v>179</v>
       </c>
@@ -8614,13 +8609,13 @@
         <v>500</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J179" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K179" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L179" s="1" t="n">
         <v>1</v>
@@ -8632,7 +8627,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="n">
         <v>180</v>
       </c>
@@ -8658,13 +8653,13 @@
         <v>500</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J180" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K180" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L180" s="1" t="n">
         <v>1</v>
@@ -8676,7 +8671,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="n">
         <v>181</v>
       </c>
@@ -8702,13 +8697,13 @@
         <v>500</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J181" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K181" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L181" s="1" t="n">
         <v>1</v>
@@ -8720,7 +8715,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="n">
         <v>182</v>
       </c>
@@ -8746,13 +8741,13 @@
         <v>500</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J182" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K182" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L182" s="1" t="n">
         <v>1</v>
@@ -8764,7 +8759,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="n">
         <v>183</v>
       </c>
@@ -8790,13 +8785,13 @@
         <v>500</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J183" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K183" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L183" s="1" t="n">
         <v>1</v>
@@ -8808,7 +8803,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="n">
         <v>184</v>
       </c>
@@ -8835,13 +8830,13 @@
         <v>500</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J184" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K184" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L184" s="1" t="n">
         <v>1</v>
@@ -8853,7 +8848,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="n">
         <v>185</v>
       </c>
@@ -8880,13 +8875,13 @@
         <v>500</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J185" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K185" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L185" s="1" t="n">
         <v>1</v>
@@ -8898,7 +8893,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="n">
         <v>186</v>
       </c>
@@ -8925,13 +8920,13 @@
         <v>500</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J186" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K186" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L186" s="1" t="n">
         <v>1</v>
@@ -8943,7 +8938,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="n">
         <v>187</v>
       </c>
@@ -8970,13 +8965,13 @@
         <v>500</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J187" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K187" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L187" s="1" t="n">
         <v>1</v>
@@ -8988,7 +8983,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="n">
         <v>188</v>
       </c>
@@ -9015,13 +9010,13 @@
         <v>500</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J188" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K188" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L188" s="1" t="n">
         <v>1</v>
@@ -9033,7 +9028,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="n">
         <v>189</v>
       </c>
@@ -9060,13 +9055,13 @@
         <v>500</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J189" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K189" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L189" s="1" t="n">
         <v>1</v>
@@ -9078,7 +9073,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="n">
         <v>190</v>
       </c>
@@ -9105,13 +9100,13 @@
         <v>500</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J190" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K190" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L190" s="1" t="n">
         <v>1</v>
@@ -9123,7 +9118,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="n">
         <v>191</v>
       </c>
@@ -9150,13 +9145,13 @@
         <v>500</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J191" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K191" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L191" s="1" t="n">
         <v>1</v>
@@ -9168,7 +9163,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="n">
         <v>192</v>
       </c>
@@ -9195,13 +9190,13 @@
         <v>500</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J192" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K192" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L192" s="1" t="n">
         <v>1</v>
@@ -9213,7 +9208,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="n">
         <v>193</v>
       </c>
@@ -9240,13 +9235,13 @@
         <v>500</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J193" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K193" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L193" s="1" t="n">
         <v>1</v>
@@ -9258,7 +9253,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="n">
         <v>194</v>
       </c>
@@ -9285,13 +9280,13 @@
         <v>500</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J194" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K194" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L194" s="1" t="n">
         <v>1</v>
@@ -9303,7 +9298,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="n">
         <v>195</v>
       </c>
@@ -9330,13 +9325,13 @@
         <v>500</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J195" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K195" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L195" s="1" t="n">
         <v>1</v>
@@ -9348,7 +9343,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="n">
         <v>196</v>
       </c>
@@ -9375,13 +9370,13 @@
         <v>500</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J196" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K196" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L196" s="1" t="n">
         <v>1</v>
@@ -9393,7 +9388,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="n">
         <v>197</v>
       </c>
@@ -9420,13 +9415,13 @@
         <v>500</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J197" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K197" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L197" s="1" t="n">
         <v>1</v>
@@ -9438,7 +9433,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="n">
         <v>198</v>
       </c>
@@ -9465,13 +9460,13 @@
         <v>500</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J198" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K198" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L198" s="1" t="n">
         <v>1</v>
@@ -9483,7 +9478,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="n">
         <v>199</v>
       </c>
@@ -9510,13 +9505,13 @@
         <v>500</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J199" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K199" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L199" s="1" t="n">
         <v>1</v>
@@ -9528,7 +9523,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="n">
         <v>200</v>
       </c>
@@ -9555,13 +9550,13 @@
         <v>500</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J200" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K200" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L200" s="1" t="n">
         <v>1</v>
@@ -9573,7 +9568,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="n">
         <v>201</v>
       </c>
@@ -9599,13 +9594,13 @@
         <v>500</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J201" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K201" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L201" s="1" t="n">
         <v>1</v>
@@ -9617,7 +9612,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="n">
         <v>202</v>
       </c>
@@ -9643,13 +9638,13 @@
         <v>500</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J202" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K202" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L202" s="1" t="n">
         <v>1</v>
@@ -9661,7 +9656,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="n">
         <v>203</v>
       </c>
@@ -9687,13 +9682,13 @@
         <v>500</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J203" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K203" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L203" s="1" t="n">
         <v>1</v>
@@ -9705,7 +9700,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="n">
         <v>204</v>
       </c>
@@ -9731,13 +9726,13 @@
         <v>500</v>
       </c>
       <c r="I204" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J204" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K204" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L204" s="1" t="n">
         <v>1</v>
@@ -9749,7 +9744,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="n">
         <v>205</v>
       </c>
@@ -9775,13 +9770,13 @@
         <v>500</v>
       </c>
       <c r="I205" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J205" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K205" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L205" s="1" t="n">
         <v>1</v>
@@ -9793,7 +9788,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="n">
         <v>206</v>
       </c>
@@ -9819,13 +9814,13 @@
         <v>500</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J206" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K206" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L206" s="1" t="n">
         <v>1</v>
@@ -9837,7 +9832,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="n">
         <v>207</v>
       </c>
@@ -9863,13 +9858,13 @@
         <v>500</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J207" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K207" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L207" s="1" t="n">
         <v>1</v>
@@ -9881,7 +9876,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="n">
         <v>208</v>
       </c>
@@ -9907,13 +9902,13 @@
         <v>500</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J208" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K208" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L208" s="1" t="n">
         <v>1</v>
@@ -9925,7 +9920,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="n">
         <v>209</v>
       </c>
@@ -9951,13 +9946,13 @@
         <v>500</v>
       </c>
       <c r="I209" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J209" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K209" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L209" s="1" t="n">
         <v>1</v>
@@ -9969,7 +9964,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="n">
         <v>210</v>
       </c>
@@ -9995,13 +9990,13 @@
         <v>500</v>
       </c>
       <c r="I210" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J210" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K210" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L210" s="1" t="n">
         <v>1</v>
@@ -10013,7 +10008,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="1" t="n">
         <v>211</v>
       </c>
@@ -10040,13 +10035,13 @@
         <v>500</v>
       </c>
       <c r="I211" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J211" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K211" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L211" s="1" t="n">
         <v>1</v>
@@ -10058,7 +10053,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="1" t="n">
         <v>212</v>
       </c>
@@ -10085,13 +10080,13 @@
         <v>500</v>
       </c>
       <c r="I212" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J212" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K212" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L212" s="1" t="n">
         <v>1</v>
@@ -10103,7 +10098,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="1" t="n">
         <v>213</v>
       </c>
@@ -10130,13 +10125,13 @@
         <v>500</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J213" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K213" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L213" s="1" t="n">
         <v>1</v>
@@ -10148,7 +10143,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="1" t="n">
         <v>214</v>
       </c>
@@ -10175,13 +10170,13 @@
         <v>500</v>
       </c>
       <c r="I214" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J214" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K214" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L214" s="1" t="n">
         <v>1</v>
@@ -10193,7 +10188,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="1" t="n">
         <v>215</v>
       </c>
@@ -10220,13 +10215,13 @@
         <v>500</v>
       </c>
       <c r="I215" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J215" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K215" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L215" s="1" t="n">
         <v>1</v>
@@ -10238,7 +10233,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="1" t="n">
         <v>216</v>
       </c>
@@ -10265,13 +10260,13 @@
         <v>500</v>
       </c>
       <c r="I216" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J216" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K216" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L216" s="1" t="n">
         <v>1</v>
@@ -10283,7 +10278,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="1" t="n">
         <v>217</v>
       </c>
@@ -10310,13 +10305,13 @@
         <v>500</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J217" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K217" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L217" s="1" t="n">
         <v>1</v>
@@ -10328,7 +10323,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="1" t="n">
         <v>218</v>
       </c>
@@ -10355,13 +10350,13 @@
         <v>500</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J218" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K218" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L218" s="1" t="n">
         <v>1</v>
@@ -10373,7 +10368,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="1" t="n">
         <v>219</v>
       </c>
@@ -10400,13 +10395,13 @@
         <v>500</v>
       </c>
       <c r="I219" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J219" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K219" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L219" s="1" t="n">
         <v>1</v>
@@ -10418,7 +10413,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="1" t="n">
         <v>220</v>
       </c>
@@ -10445,13 +10440,13 @@
         <v>500</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J220" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K220" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L220" s="1" t="n">
         <v>1</v>
@@ -10463,7 +10458,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="1" t="n">
         <v>221</v>
       </c>
@@ -10490,13 +10485,13 @@
         <v>500</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J221" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K221" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L221" s="1" t="n">
         <v>1</v>
@@ -10508,7 +10503,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="1" t="n">
         <v>222</v>
       </c>
@@ -10535,13 +10530,13 @@
         <v>500</v>
       </c>
       <c r="I222" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J222" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K222" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L222" s="1" t="n">
         <v>1</v>
@@ -10553,7 +10548,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="n">
         <v>223</v>
       </c>
@@ -10580,13 +10575,13 @@
         <v>500</v>
       </c>
       <c r="I223" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J223" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K223" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L223" s="1" t="n">
         <v>1</v>
@@ -10598,7 +10593,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="n">
         <v>224</v>
       </c>
@@ -10625,13 +10620,13 @@
         <v>500</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J224" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K224" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L224" s="1" t="n">
         <v>1</v>
@@ -10643,7 +10638,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="1" t="n">
         <v>225</v>
       </c>
@@ -10670,13 +10665,13 @@
         <v>500</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J225" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K225" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L225" s="1" t="n">
         <v>1</v>
@@ -10688,7 +10683,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="1" t="n">
         <v>226</v>
       </c>
@@ -10715,13 +10710,13 @@
         <v>500</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J226" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K226" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L226" s="1" t="n">
         <v>1</v>
@@ -10733,7 +10728,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="1" t="n">
         <v>227</v>
       </c>
@@ -10760,13 +10755,13 @@
         <v>500</v>
       </c>
       <c r="I227" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J227" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K227" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L227" s="1" t="n">
         <v>1</v>
@@ -10778,7 +10773,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="1" t="n">
         <v>228</v>
       </c>
@@ -10804,13 +10799,13 @@
         <v>500</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J228" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K228" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L228" s="1" t="n">
         <v>1</v>
@@ -10822,7 +10817,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="1" t="n">
         <v>229</v>
       </c>
@@ -10848,13 +10843,13 @@
         <v>500</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J229" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K229" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L229" s="1" t="n">
         <v>1</v>
@@ -10866,7 +10861,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="1" t="n">
         <v>230</v>
       </c>
@@ -10892,13 +10887,13 @@
         <v>500</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J230" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K230" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L230" s="1" t="n">
         <v>1</v>
@@ -10910,7 +10905,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="1" t="n">
         <v>231</v>
       </c>
@@ -10936,13 +10931,13 @@
         <v>500</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J231" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K231" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L231" s="1" t="n">
         <v>1</v>
@@ -10954,7 +10949,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="1" t="n">
         <v>232</v>
       </c>
@@ -10980,13 +10975,13 @@
         <v>500</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J232" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K232" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L232" s="1" t="n">
         <v>1</v>
@@ -10998,7 +10993,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="1" t="n">
         <v>233</v>
       </c>
@@ -11024,13 +11019,13 @@
         <v>500</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J233" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K233" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L233" s="1" t="n">
         <v>1</v>
@@ -11042,7 +11037,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="n">
         <v>234</v>
       </c>
@@ -11068,13 +11063,13 @@
         <v>500</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J234" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K234" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L234" s="1" t="n">
         <v>1</v>
@@ -11086,7 +11081,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="1" t="n">
         <v>235</v>
       </c>
@@ -11112,13 +11107,13 @@
         <v>500</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J235" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K235" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L235" s="1" t="n">
         <v>1</v>
@@ -11130,7 +11125,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="n">
         <v>236</v>
       </c>
@@ -11156,13 +11151,13 @@
         <v>500</v>
       </c>
       <c r="I236" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J236" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K236" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L236" s="1" t="n">
         <v>1</v>
@@ -11174,7 +11169,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="1" t="n">
         <v>237</v>
       </c>
@@ -11200,13 +11195,13 @@
         <v>500</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J237" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K237" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L237" s="1" t="n">
         <v>1</v>
@@ -11218,7 +11213,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="1" t="n">
         <v>238</v>
       </c>
@@ -11245,13 +11240,13 @@
         <v>500</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J238" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K238" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L238" s="1" t="n">
         <v>1</v>
@@ -11263,7 +11258,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="1" t="n">
         <v>239</v>
       </c>
@@ -11290,13 +11285,13 @@
         <v>500</v>
       </c>
       <c r="I239" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J239" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K239" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L239" s="1" t="n">
         <v>1</v>
@@ -11308,7 +11303,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="1" t="n">
         <v>240</v>
       </c>
@@ -11335,13 +11330,13 @@
         <v>500</v>
       </c>
       <c r="I240" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J240" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K240" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L240" s="1" t="n">
         <v>1</v>
@@ -11353,7 +11348,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="1" t="n">
         <v>241</v>
       </c>
@@ -11380,13 +11375,13 @@
         <v>500</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J241" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K241" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L241" s="1" t="n">
         <v>1</v>
@@ -11398,7 +11393,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="1" t="n">
         <v>242</v>
       </c>
@@ -11425,13 +11420,13 @@
         <v>500</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J242" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K242" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L242" s="1" t="n">
         <v>1</v>
@@ -11443,7 +11438,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="1" t="n">
         <v>243</v>
       </c>
@@ -11470,13 +11465,13 @@
         <v>500</v>
       </c>
       <c r="I243" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J243" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K243" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L243" s="1" t="n">
         <v>1</v>
@@ -11488,7 +11483,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="1" t="n">
         <v>244</v>
       </c>
@@ -11515,13 +11510,13 @@
         <v>500</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J244" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K244" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L244" s="1" t="n">
         <v>1</v>
@@ -11533,7 +11528,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="n">
         <v>245</v>
       </c>
@@ -11560,13 +11555,13 @@
         <v>500</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J245" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K245" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L245" s="1" t="n">
         <v>1</v>
@@ -11578,7 +11573,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="n">
         <v>246</v>
       </c>
@@ -11605,13 +11600,13 @@
         <v>500</v>
       </c>
       <c r="I246" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J246" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K246" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L246" s="1" t="n">
         <v>1</v>
@@ -11623,7 +11618,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="1" t="n">
         <v>247</v>
       </c>
@@ -11650,13 +11645,13 @@
         <v>500</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J247" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K247" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L247" s="1" t="n">
         <v>1</v>
@@ -11668,7 +11663,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="1" t="n">
         <v>248</v>
       </c>
@@ -11695,13 +11690,13 @@
         <v>500</v>
       </c>
       <c r="I248" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J248" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K248" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L248" s="1" t="n">
         <v>1</v>
@@ -11713,7 +11708,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="1" t="n">
         <v>249</v>
       </c>
@@ -11740,13 +11735,13 @@
         <v>500</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J249" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K249" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L249" s="1" t="n">
         <v>1</v>
@@ -11758,7 +11753,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="1" t="n">
         <v>250</v>
       </c>
@@ -11785,13 +11780,13 @@
         <v>500</v>
       </c>
       <c r="I250" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J250" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K250" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L250" s="1" t="n">
         <v>1</v>
@@ -11803,7 +11798,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="1" t="n">
         <v>251</v>
       </c>
@@ -11830,13 +11825,13 @@
         <v>500</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J251" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K251" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L251" s="1" t="n">
         <v>1</v>
@@ -11848,7 +11843,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="1" t="n">
         <v>252</v>
       </c>
@@ -11875,13 +11870,13 @@
         <v>500</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J252" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K252" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L252" s="1" t="n">
         <v>1</v>
@@ -11893,7 +11888,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="1" t="n">
         <v>253</v>
       </c>
@@ -11920,13 +11915,13 @@
         <v>500</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J253" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K253" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L253" s="1" t="n">
         <v>1</v>
@@ -11938,7 +11933,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="1" t="n">
         <v>254</v>
       </c>
@@ -11965,13 +11960,13 @@
         <v>500</v>
       </c>
       <c r="I254" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J254" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K254" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L254" s="1" t="n">
         <v>1</v>
@@ -11983,7 +11978,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="255" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="1" t="n">
         <v>255</v>
       </c>
@@ -12009,13 +12004,13 @@
         <v>500</v>
       </c>
       <c r="I255" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J255" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K255" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L255" s="1" t="n">
         <v>1</v>
@@ -12027,7 +12022,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="1" t="n">
         <v>256</v>
       </c>
@@ -12053,13 +12048,13 @@
         <v>500</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J256" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K256" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L256" s="1" t="n">
         <v>1</v>
@@ -12071,7 +12066,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="1" t="n">
         <v>257</v>
       </c>
@@ -12097,13 +12092,13 @@
         <v>500</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J257" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K257" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L257" s="1" t="n">
         <v>1</v>
@@ -12115,7 +12110,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="1" t="n">
         <v>258</v>
       </c>
@@ -12141,13 +12136,13 @@
         <v>500</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J258" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K258" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L258" s="1" t="n">
         <v>1</v>
@@ -12159,7 +12154,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="259" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="1" t="n">
         <v>259</v>
       </c>
@@ -12185,13 +12180,13 @@
         <v>500</v>
       </c>
       <c r="I259" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J259" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K259" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L259" s="1" t="n">
         <v>1</v>
@@ -12203,7 +12198,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="260" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="1" t="n">
         <v>260</v>
       </c>
@@ -12229,13 +12224,13 @@
         <v>500</v>
       </c>
       <c r="I260" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J260" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K260" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L260" s="1" t="n">
         <v>1</v>
@@ -12247,7 +12242,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="261" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="1" t="n">
         <v>261</v>
       </c>
@@ -12273,13 +12268,13 @@
         <v>500</v>
       </c>
       <c r="I261" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J261" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K261" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L261" s="1" t="n">
         <v>1</v>
@@ -12291,7 +12286,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="262" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="1" t="n">
         <v>262</v>
       </c>
@@ -12317,13 +12312,13 @@
         <v>500</v>
       </c>
       <c r="I262" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J262" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K262" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L262" s="1" t="n">
         <v>1</v>
@@ -12335,7 +12330,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="263" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="1" t="n">
         <v>263</v>
       </c>
@@ -12361,13 +12356,13 @@
         <v>500</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J263" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K263" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L263" s="1" t="n">
         <v>1</v>
@@ -12379,7 +12374,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="1" t="n">
         <v>264</v>
       </c>
@@ -12405,13 +12400,13 @@
         <v>500</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J264" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K264" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L264" s="1" t="n">
         <v>1</v>
@@ -12423,7 +12418,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="265" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="1" t="n">
         <v>265</v>
       </c>
@@ -12450,13 +12445,13 @@
         <v>500</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J265" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K265" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L265" s="1" t="n">
         <v>1</v>
@@ -12468,7 +12463,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="1" t="n">
         <v>266</v>
       </c>
@@ -12495,13 +12490,13 @@
         <v>500</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J266" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K266" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L266" s="1" t="n">
         <v>1</v>
@@ -12513,7 +12508,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="267" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="1" t="n">
         <v>267</v>
       </c>
@@ -12540,13 +12535,13 @@
         <v>500</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J267" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K267" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L267" s="1" t="n">
         <v>1</v>
@@ -12558,7 +12553,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="268" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="n">
         <v>268</v>
       </c>
@@ -12585,13 +12580,13 @@
         <v>500</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J268" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K268" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L268" s="1" t="n">
         <v>1</v>
@@ -12603,7 +12598,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="269" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="n">
         <v>269</v>
       </c>
@@ -12630,13 +12625,13 @@
         <v>500</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J269" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K269" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L269" s="1" t="n">
         <v>1</v>
@@ -12648,7 +12643,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="270" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="1" t="n">
         <v>270</v>
       </c>
@@ -12675,13 +12670,13 @@
         <v>500</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J270" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K270" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L270" s="1" t="n">
         <v>1</v>
@@ -12693,7 +12688,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="271" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="1" t="n">
         <v>271</v>
       </c>
@@ -12720,13 +12715,13 @@
         <v>500</v>
       </c>
       <c r="I271" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J271" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K271" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L271" s="1" t="n">
         <v>1</v>
@@ -12738,7 +12733,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="272" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="1" t="n">
         <v>272</v>
       </c>
@@ -12765,13 +12760,13 @@
         <v>500</v>
       </c>
       <c r="I272" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J272" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K272" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L272" s="1" t="n">
         <v>1</v>
@@ -12783,7 +12778,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="273" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="1" t="n">
         <v>273</v>
       </c>
@@ -12810,13 +12805,13 @@
         <v>500</v>
       </c>
       <c r="I273" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J273" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K273" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L273" s="1" t="n">
         <v>1</v>
@@ -12828,7 +12823,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="274" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="1" t="n">
         <v>274</v>
       </c>
@@ -12855,13 +12850,13 @@
         <v>500</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J274" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K274" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L274" s="1" t="n">
         <v>1</v>
@@ -12873,7 +12868,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="275" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="1" t="n">
         <v>275</v>
       </c>
@@ -12900,13 +12895,13 @@
         <v>500</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J275" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K275" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L275" s="1" t="n">
         <v>1</v>
@@ -12918,7 +12913,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="1" t="n">
         <v>276</v>
       </c>
@@ -12945,13 +12940,13 @@
         <v>500</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J276" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K276" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L276" s="1" t="n">
         <v>1</v>
@@ -12963,7 +12958,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="1" t="n">
         <v>277</v>
       </c>
@@ -12990,13 +12985,13 @@
         <v>500</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J277" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K277" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L277" s="1" t="n">
         <v>1</v>
@@ -13008,7 +13003,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="1" t="n">
         <v>278</v>
       </c>
@@ -13035,13 +13030,13 @@
         <v>500</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J278" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K278" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L278" s="1" t="n">
         <v>1</v>
@@ -13053,7 +13048,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="1" t="n">
         <v>279</v>
       </c>
@@ -13080,13 +13075,13 @@
         <v>500</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J279" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K279" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L279" s="1" t="n">
         <v>1</v>
@@ -13098,7 +13093,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="280" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="1" t="n">
         <v>280</v>
       </c>
@@ -13125,13 +13120,13 @@
         <v>500</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J280" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K280" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L280" s="1" t="n">
         <v>1</v>
@@ -13143,7 +13138,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="1" t="n">
         <v>281</v>
       </c>
@@ -13170,13 +13165,13 @@
         <v>500</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J281" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K281" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L281" s="1" t="n">
         <v>1</v>
@@ -13188,7 +13183,7 @@
         <v>46206.6655439815</v>
       </c>
     </row>
-    <row r="282" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="1" t="n">
         <v>282</v>
       </c>
@@ -13209,16 +13204,16 @@
         <v>5340</v>
       </c>
       <c r="H282" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J282" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K282" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L282" s="1" t="n">
         <v>1</v>
@@ -13230,7 +13225,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="1" t="n">
         <v>283</v>
       </c>
@@ -13251,16 +13246,16 @@
         <v>5785</v>
       </c>
       <c r="H283" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J283" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K283" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L283" s="1" t="n">
         <v>1</v>
@@ -13272,7 +13267,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="1" t="n">
         <v>284</v>
       </c>
@@ -13293,16 +13288,16 @@
         <v>6230</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I284" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J284" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K284" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L284" s="1" t="n">
         <v>1</v>
@@ -13314,7 +13309,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="285" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="285" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="1" t="n">
         <v>285</v>
       </c>
@@ -13335,16 +13330,16 @@
         <v>6675</v>
       </c>
       <c r="H285" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I285" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J285" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K285" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L285" s="1" t="n">
         <v>1</v>
@@ -13356,7 +13351,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="286" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="1" t="n">
         <v>286</v>
       </c>
@@ -13377,16 +13372,16 @@
         <v>7120</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J286" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K286" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L286" s="1" t="n">
         <v>1</v>
@@ -13398,7 +13393,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="287" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="1" t="n">
         <v>287</v>
       </c>
@@ -13419,16 +13414,16 @@
         <v>7395</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J287" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K287" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L287" s="1" t="n">
         <v>1</v>
@@ -13440,7 +13435,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="288" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="1" t="n">
         <v>288</v>
       </c>
@@ -13461,16 +13456,16 @@
         <v>7830</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I288" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J288" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K288" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L288" s="1" t="n">
         <v>1</v>
@@ -13482,7 +13477,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="289" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="1" t="n">
         <v>289</v>
       </c>
@@ -13503,16 +13498,16 @@
         <v>8265</v>
       </c>
       <c r="H289" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J289" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K289" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L289" s="1" t="n">
         <v>1</v>
@@ -13524,7 +13519,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="290" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="n">
         <v>290</v>
       </c>
@@ -13545,16 +13540,16 @@
         <v>8700</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J290" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K290" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L290" s="1" t="n">
         <v>1</v>
@@ -13566,7 +13561,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="291" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="n">
         <v>291</v>
       </c>
@@ -13587,16 +13582,16 @@
         <v>9135</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J291" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K291" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L291" s="1" t="n">
         <v>1</v>
@@ -13608,7 +13603,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="292" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="292" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="1" t="n">
         <v>292</v>
       </c>
@@ -13629,16 +13624,16 @@
         <v>9350</v>
       </c>
       <c r="H292" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I292" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J292" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K292" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L292" s="1" t="n">
         <v>1</v>
@@ -13650,7 +13645,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="293" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="1" t="n">
         <v>293</v>
       </c>
@@ -13671,16 +13666,16 @@
         <v>9775</v>
       </c>
       <c r="H293" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I293" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J293" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K293" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L293" s="1" t="n">
         <v>1</v>
@@ -13692,7 +13687,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="294" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="294" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="1" t="n">
         <v>294</v>
       </c>
@@ -13713,16 +13708,16 @@
         <v>10200</v>
       </c>
       <c r="H294" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I294" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J294" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K294" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L294" s="1" t="n">
         <v>1</v>
@@ -13734,7 +13729,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="295" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="295" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="1" t="n">
         <v>295</v>
       </c>
@@ -13755,16 +13750,16 @@
         <v>10625</v>
       </c>
       <c r="H295" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I295" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J295" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K295" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L295" s="1" t="n">
         <v>1</v>
@@ -13776,7 +13771,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="296" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="1" t="n">
         <v>296</v>
       </c>
@@ -13797,16 +13792,16 @@
         <v>11050</v>
       </c>
       <c r="H296" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I296" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J296" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K296" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L296" s="1" t="n">
         <v>1</v>
@@ -13818,7 +13813,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="297" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="1" t="n">
         <v>297</v>
       </c>
@@ -13839,16 +13834,16 @@
         <v>11070</v>
       </c>
       <c r="H297" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I297" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J297" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K297" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L297" s="1" t="n">
         <v>1</v>
@@ -13860,7 +13855,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="298" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="298" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="1" t="n">
         <v>298</v>
       </c>
@@ -13881,16 +13876,16 @@
         <v>11480</v>
       </c>
       <c r="H298" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I298" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J298" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K298" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L298" s="1" t="n">
         <v>1</v>
@@ -13902,7 +13897,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="299" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="1" t="n">
         <v>299</v>
       </c>
@@ -13923,16 +13918,16 @@
         <v>11890</v>
       </c>
       <c r="H299" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I299" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J299" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K299" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L299" s="1" t="n">
         <v>1</v>
@@ -13944,7 +13939,7 @@
         <v>46198.723599537</v>
       </c>
     </row>
-    <row r="300" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="1" t="n">
         <v>300</v>
       </c>
@@ -13965,16 +13960,16 @@
         <v>12300</v>
       </c>
       <c r="H300" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I300" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J300" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K300" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L300" s="1" t="n">
         <v>1</v>
@@ -13987,13 +13982,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N300">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="8"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:N300"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -14028,37 +14017,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="J1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14066,37 +14055,37 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="J2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14104,37 +14093,37 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>93</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H3" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="L3" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14142,37 +14131,37 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="H4" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F4" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H4" s="12" t="s">
+      <c r="J4" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="K4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14180,37 +14169,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>64</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H5" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14218,37 +14207,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>65</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H6" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14256,37 +14245,37 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H7" s="12" t="s">
+      <c r="J7" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14294,37 +14283,37 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="12" t="s">
+      <c r="J8" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="K8" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
